--- a/cell_sim/data/Mycoplasma_pneumoniae/input_data/kinetic_params.xlsx
+++ b/cell_sim/data/Mycoplasma_pneumoniae/input_data/kinetic_params.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,9 @@
           <t>MPN078</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -553,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -561,7 +563,9 @@
           <t>MPN079</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -606,7 +610,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -614,7 +618,9 @@
           <t>MPN025</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -659,7 +665,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -667,7 +673,9 @@
           <t>MPN564</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -712,7 +720,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -720,7 +728,9 @@
           <t>MPN078</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -765,7 +775,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -773,7 +783,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -818,7 +830,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -826,7 +838,9 @@
           <t>MPN651/MPN653</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -871,7 +885,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -879,7 +893,9 @@
           <t>MPN652</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -924,7 +940,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -932,7 +948,9 @@
           <t>MPN494-MPN496</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -977,7 +995,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -985,7 +1003,9 @@
           <t>MPN497</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1030,7 +1050,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1038,7 +1058,9 @@
           <t>MPN493</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1083,7 +1105,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1091,7 +1113,9 @@
           <t>MPN492</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1136,7 +1160,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1144,7 +1168,9 @@
           <t>MPN498</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1189,7 +1215,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1197,7 +1223,9 @@
           <t>MPN564</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1242,7 +1270,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1250,7 +1278,9 @@
           <t>MPN043</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1295,7 +1325,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1303,7 +1333,9 @@
           <t>MPN050</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1348,7 +1380,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1356,7 +1388,9 @@
           <t>MPN133-MPN136</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1472,7 +1506,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1480,7 +1514,9 @@
           <t>MPN321;MPN300</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1525,7 +1561,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1533,7 +1569,9 @@
           <t>MPN321;MPN300</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1578,7 +1616,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1586,7 +1624,9 @@
           <t>MPN017</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1631,7 +1671,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1639,7 +1679,9 @@
           <t>MPN017</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1684,7 +1726,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1692,7 +1734,9 @@
           <t>MPN543</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1737,7 +1781,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1745,7 +1789,9 @@
           <t>MPN576</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1790,7 +1836,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1798,7 +1844,9 @@
           <t>MPN017</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1843,7 +1891,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1851,7 +1899,9 @@
           <t>MPN348</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1896,7 +1946,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1904,7 +1954,9 @@
           <t>MPN576</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -1949,7 +2001,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1957,7 +2009,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2002,7 +2056,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2010,7 +2064,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2055,7 +2111,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2063,7 +2119,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2179,7 +2237,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2187,7 +2245,9 @@
           <t>MPN258-MPN260</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2232,7 +2292,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2240,7 +2300,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2285,7 +2347,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2293,7 +2355,9 @@
           <t>MPN082</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2338,7 +2402,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2346,7 +2410,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2391,7 +2457,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2399,7 +2465,9 @@
           <t>MPN082</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2444,7 +2512,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2452,7 +2520,9 @@
           <t>MPN251</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2497,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2505,7 +2575,9 @@
           <t>MPN595</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2550,7 +2622,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2558,7 +2630,9 @@
           <t>MPN073</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2603,7 +2677,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2611,7 +2685,9 @@
           <t>MPN066</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2656,7 +2732,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2664,7 +2740,9 @@
           <t>MPN066</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2709,7 +2787,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2717,7 +2795,9 @@
           <t>MPN063</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2833,7 +2913,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2841,7 +2921,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2886,7 +2968,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2894,7 +2976,9 @@
           <t>MPN434/MPN002/MPN120</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2939,7 +3023,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2947,7 +3031,9 @@
           <t>MPN573/MPN574</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -2992,7 +3078,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3000,7 +3086,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3045,7 +3133,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3053,7 +3141,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3169,7 +3259,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3177,7 +3267,9 @@
           <t>MPN674</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3222,7 +3314,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3230,7 +3322,9 @@
           <t>MPN392/MPN393</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3275,7 +3369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3283,7 +3377,9 @@
           <t>MPN391</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3328,7 +3424,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3336,7 +3432,9 @@
           <t>MPN390</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3381,7 +3479,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3389,7 +3487,9 @@
           <t>MPN428</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3434,7 +3534,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3442,7 +3542,9 @@
           <t>MPN533</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3487,7 +3589,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3495,7 +3597,9 @@
           <t>MPN394</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3540,7 +3644,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3548,7 +3652,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3593,7 +3699,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3601,7 +3707,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3713,11 +3821,13 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3738,11 +3848,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3842,7 +3954,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3850,7 +3962,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3895,7 +4009,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3903,7 +4017,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -3948,7 +4064,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3956,7 +4072,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4001,7 +4119,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4009,7 +4127,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4054,7 +4174,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4062,7 +4182,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4107,7 +4229,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4115,7 +4237,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4160,7 +4284,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4168,7 +4292,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4213,7 +4339,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4221,7 +4347,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4266,7 +4394,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4274,7 +4402,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4319,7 +4449,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4327,7 +4457,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4372,7 +4504,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4380,7 +4512,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4425,7 +4559,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4433,7 +4567,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4478,7 +4614,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4486,7 +4622,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4531,7 +4669,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4539,7 +4677,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4584,7 +4724,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4592,7 +4732,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4637,7 +4779,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4645,7 +4787,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4690,7 +4834,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4698,7 +4842,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4743,7 +4889,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4751,7 +4897,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4796,7 +4944,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4804,7 +4952,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4849,7 +4999,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4857,7 +5007,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4902,7 +5054,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4910,7 +5062,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -4955,7 +5109,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4963,7 +5117,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5008,7 +5164,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5016,7 +5172,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5061,7 +5219,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5069,7 +5227,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5114,7 +5274,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5122,7 +5282,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5167,7 +5329,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5175,7 +5337,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5220,7 +5384,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5228,7 +5392,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5273,7 +5439,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5281,7 +5447,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5326,7 +5494,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5334,7 +5502,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5379,7 +5549,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5387,7 +5557,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>100</v>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5432,7 +5604,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5440,7 +5612,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5485,7 +5659,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5493,7 +5667,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5538,7 +5714,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5546,7 +5722,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5591,7 +5769,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5599,7 +5777,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5644,7 +5824,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5652,7 +5832,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5697,7 +5879,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5705,7 +5887,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5750,7 +5934,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5758,7 +5942,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>100</v>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5803,7 +5989,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5811,7 +5997,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>100</v>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5856,7 +6044,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5864,7 +6052,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>100</v>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5909,7 +6099,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5917,7 +6107,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -5962,7 +6154,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5970,7 +6162,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6015,7 +6209,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6023,7 +6217,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6068,7 +6264,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6076,7 +6272,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>100</v>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6121,7 +6319,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6129,7 +6327,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>100</v>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6174,7 +6374,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6182,7 +6382,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>100</v>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6227,7 +6429,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6235,7 +6437,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>100</v>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6280,7 +6484,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6288,7 +6492,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>100</v>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6333,7 +6539,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6341,7 +6547,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>100</v>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6386,7 +6594,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6394,7 +6602,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>100</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6439,7 +6649,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6447,7 +6657,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>100</v>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6492,7 +6704,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6500,7 +6712,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>100</v>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6545,7 +6759,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6553,7 +6767,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6598,7 +6814,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6606,7 +6822,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>100</v>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6651,7 +6869,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6659,7 +6877,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>100</v>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6704,7 +6924,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6712,7 +6932,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6757,7 +6979,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6765,7 +6987,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>100</v>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6810,7 +7034,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6818,7 +7042,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>100</v>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6863,7 +7089,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6871,7 +7097,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>100</v>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -6987,7 +7215,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6995,7 +7223,9 @@
           <t>MPN304/MPN305;MPN560</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7040,7 +7270,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7048,7 +7278,9 @@
           <t>MPN306</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7093,7 +7325,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7101,7 +7333,9 @@
           <t>MPN307</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7146,7 +7380,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7154,7 +7388,9 @@
           <t>MPN060</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7199,7 +7435,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7207,7 +7443,9 @@
           <t>MPN108</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7252,7 +7490,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7260,7 +7498,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7305,7 +7545,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7313,7 +7553,9 @@
           <t>MPN236-MPN238</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7358,7 +7600,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7366,7 +7608,9 @@
           <t>MPN236-MPN238</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7411,7 +7655,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7419,7 +7663,9 @@
           <t>MPN023</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7464,7 +7710,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7472,7 +7718,9 @@
           <t>MPN520</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7517,7 +7765,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7525,7 +7773,9 @@
           <t>MPN480</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7570,7 +7820,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7578,7 +7828,9 @@
           <t>MPN384</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7623,7 +7875,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7631,7 +7883,9 @@
           <t>MPN356</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7676,7 +7930,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7684,7 +7938,9 @@
           <t>MPN678</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7729,7 +7985,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7737,7 +7993,9 @@
           <t>MPN678</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7782,7 +8040,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7790,7 +8048,9 @@
           <t>MPN556</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7835,7 +8095,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7843,7 +8103,9 @@
           <t>MPN669</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7888,7 +8150,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7896,7 +8158,9 @@
           <t>MPN265</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7941,7 +8205,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7949,7 +8213,9 @@
           <t>MPN005</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -7994,7 +8260,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8002,7 +8268,9 @@
           <t>MPN553</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8047,7 +8315,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8055,7 +8323,9 @@
           <t>MPN402</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8100,7 +8370,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8108,7 +8378,9 @@
           <t>MPN046</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8153,7 +8425,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8161,7 +8433,9 @@
           <t>MPN252</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8206,7 +8480,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8214,7 +8488,9 @@
           <t>MPN277</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8259,7 +8535,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8267,7 +8543,9 @@
           <t>MPN045</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8312,7 +8590,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8320,7 +8598,9 @@
           <t>MPN105/MPN106</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8365,7 +8645,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -8373,7 +8653,9 @@
           <t>MPN418</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8418,7 +8700,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8426,7 +8708,9 @@
           <t>MPN354</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8471,7 +8755,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8479,7 +8763,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8524,7 +8810,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8532,7 +8818,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>100</v>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8577,7 +8865,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -8585,7 +8873,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8630,7 +8920,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -8638,7 +8928,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8683,7 +8975,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -8691,7 +8983,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8736,7 +9030,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -8744,7 +9038,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8789,7 +9085,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -8797,7 +9093,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8842,7 +9140,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8850,7 +9148,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8895,7 +9195,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8903,7 +9203,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>100</v>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -8948,7 +9250,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8956,7 +9258,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>100</v>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9001,7 +9305,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -9009,7 +9313,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>100</v>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9054,7 +9360,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -9062,7 +9368,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9107,7 +9415,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -9115,7 +9423,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9160,7 +9470,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9168,7 +9478,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9213,7 +9525,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9221,7 +9533,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>100</v>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9266,7 +9580,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9274,7 +9588,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>100</v>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9319,7 +9635,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9327,7 +9643,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>100</v>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9372,7 +9690,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9698,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>100</v>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9425,7 +9745,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9433,7 +9753,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>100</v>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9478,7 +9800,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -9486,7 +9808,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>100</v>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9531,7 +9855,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -9539,7 +9863,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>100</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9584,7 +9910,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -9592,7 +9918,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>100</v>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9637,7 +9965,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -9645,7 +9973,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>100</v>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9690,7 +10020,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -9698,7 +10028,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9743,7 +10075,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9751,7 +10083,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>100</v>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9796,7 +10130,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9804,7 +10138,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>100</v>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9849,7 +10185,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9857,7 +10193,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9902,7 +10240,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9910,7 +10248,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>100</v>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -9955,7 +10295,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9963,7 +10303,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>100</v>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10008,7 +10350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -10016,7 +10358,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>100</v>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10061,7 +10405,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10069,7 +10413,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10114,7 +10460,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10122,7 +10468,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>100</v>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10167,7 +10515,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10175,7 +10523,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>100</v>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10220,7 +10570,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10228,7 +10578,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>100</v>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10273,7 +10625,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10281,7 +10633,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>100</v>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10326,7 +10680,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10334,7 +10688,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>100</v>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10379,7 +10735,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10387,7 +10743,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>100</v>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10432,7 +10790,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -10440,7 +10798,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>100</v>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10485,7 +10845,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -10493,7 +10853,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>100</v>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10538,7 +10900,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10546,7 +10908,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>100</v>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10591,7 +10955,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10599,7 +10963,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>100</v>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10715,7 +11081,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -10723,7 +11089,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10768,7 +11136,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10776,7 +11144,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10892,7 +11262,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -10900,7 +11270,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10945,7 +11317,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10953,7 +11325,9 @@
           <t>MPN336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -10998,7 +11372,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11006,7 +11380,9 @@
           <t>MPN382</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11051,7 +11427,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11059,7 +11435,9 @@
           <t>MPN298</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11104,7 +11482,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11112,7 +11490,9 @@
           <t>MPN479</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11157,7 +11537,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11165,7 +11545,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11210,7 +11592,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -11218,7 +11600,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11263,7 +11647,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -11271,7 +11655,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11316,7 +11702,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -11324,7 +11710,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11440,7 +11828,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -11448,7 +11836,9 @@
           <t>MPN047</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11493,7 +11883,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11501,7 +11891,9 @@
           <t>MPN336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11546,7 +11938,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11554,7 +11946,9 @@
           <t>MPN562</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11599,7 +11993,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11607,7 +12001,9 @@
           <t>MPN267</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11652,7 +12048,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11660,7 +12056,9 @@
           <t>MPN267</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11705,7 +12103,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11713,7 +12111,9 @@
           <t>MPN158</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11758,7 +12158,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -11766,7 +12166,9 @@
           <t>MPN158</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11811,7 +12213,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -11819,7 +12221,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11864,7 +12268,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -11872,7 +12276,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11917,7 +12323,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11925,7 +12331,9 @@
           <t>MPN550</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -11970,7 +12378,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -11978,7 +12386,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12023,7 +12433,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12031,7 +12441,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12076,7 +12488,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12084,7 +12496,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12129,7 +12543,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12137,7 +12551,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12182,7 +12598,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12190,7 +12606,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12235,7 +12653,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12243,7 +12661,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12288,7 +12708,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12296,7 +12716,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12341,7 +12763,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12349,7 +12771,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12394,7 +12818,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12402,7 +12826,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12447,7 +12873,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12455,7 +12881,9 @@
           <t>MPN609-MPN611</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12500,7 +12928,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12508,7 +12936,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12624,7 +13054,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -12632,7 +13062,9 @@
           <t>MPN597-MPN604</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12677,7 +13109,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12685,7 +13117,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12801,7 +13235,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -12809,7 +13243,9 @@
           <t>MPN627/MPN207</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12854,7 +13290,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12862,7 +13298,9 @@
           <t>MPN250</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12907,7 +13345,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12915,7 +13353,9 @@
           <t>MPN302</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -12960,7 +13400,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12968,7 +13408,9 @@
           <t>MPN025</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13013,7 +13455,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13021,7 +13463,9 @@
           <t>MPN629</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13066,7 +13510,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13074,7 +13518,9 @@
           <t>MPN430</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13119,7 +13565,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13127,7 +13573,9 @@
           <t>MPN429</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13172,7 +13620,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13180,7 +13628,9 @@
           <t>MPN628</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13225,7 +13675,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13233,7 +13683,9 @@
           <t>MPN606</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13278,7 +13730,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13286,7 +13738,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13402,7 +13856,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -13410,7 +13864,9 @@
           <t>MPN051</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13455,7 +13911,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13463,7 +13919,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13508,7 +13966,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -13516,7 +13974,9 @@
           <t>MPN547</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13561,7 +14021,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13569,7 +14029,9 @@
           <t>MPN350/MPN546</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13614,7 +14076,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13622,7 +14084,9 @@
           <t>MPN299</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13667,7 +14131,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13675,7 +14139,9 @@
           <t>MPN637</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13720,7 +14186,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13728,7 +14194,9 @@
           <t>MPN253</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13773,7 +14241,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13781,7 +14249,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13826,7 +14296,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13834,7 +14304,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13879,7 +14351,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13887,7 +14359,9 @@
           <t>MPN455</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13932,7 +14406,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13940,7 +14414,9 @@
           <t>MPN066</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -13985,7 +14461,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13993,7 +14469,9 @@
           <t>MPN667</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14038,7 +14516,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -14046,7 +14524,9 @@
           <t>MPN257</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14091,7 +14571,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -14099,7 +14579,9 @@
           <t>MPN483</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14144,7 +14626,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -14152,7 +14634,9 @@
           <t>MPN532</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14197,7 +14681,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -14205,7 +14689,9 @@
           <t>MPN336</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14250,7 +14736,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -14258,7 +14744,9 @@
           <t>MPN420</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14303,7 +14791,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -14311,7 +14799,9 @@
           <t>MPN445</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14356,7 +14846,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -14364,7 +14854,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14409,7 +14901,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -14417,7 +14909,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14533,7 +15027,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -14541,7 +15035,9 @@
           <t>MPN395</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14586,7 +15082,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -14594,7 +15090,9 @@
           <t>MPN062</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14639,7 +15137,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -14647,7 +15145,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14692,7 +15192,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -14700,7 +15200,9 @@
           <t>MPN185</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14745,7 +15247,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -14753,7 +15255,9 @@
           <t>MPN322-MPN324</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14798,7 +15302,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -14806,7 +15310,9 @@
           <t>MPN240</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14851,7 +15357,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14859,7 +15365,9 @@
           <t>MPN516</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14904,7 +15412,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14912,7 +15420,9 @@
           <t>MPN528</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -14957,7 +15467,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14965,7 +15475,9 @@
           <t>MPN062</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15010,7 +15522,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15018,7 +15530,9 @@
           <t>MPN386</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15063,7 +15577,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15071,7 +15585,9 @@
           <t>MPN185</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15116,7 +15632,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15124,7 +15640,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15169,7 +15687,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15177,7 +15695,9 @@
           <t>MPN429</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15222,7 +15742,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15230,7 +15750,9 @@
           <t>MPN034/MPN378</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15275,7 +15797,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15283,7 +15805,9 @@
           <t>MPN672</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15328,7 +15852,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15336,7 +15860,9 @@
           <t>MPN062</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15381,7 +15907,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15389,7 +15915,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15434,7 +15962,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15442,7 +15970,9 @@
           <t>MPN246</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15487,7 +16017,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15495,7 +16025,9 @@
           <t>MPN322-MPN324</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15540,7 +16072,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15548,7 +16080,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15593,7 +16127,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15601,7 +16135,9 @@
           <t>MPN429</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15646,7 +16182,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -15654,7 +16190,9 @@
           <t>MPN062</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15699,7 +16237,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15707,7 +16245,9 @@
           <t>MPN386</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15752,7 +16292,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15760,7 +16300,9 @@
           <t>MPN246</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15805,7 +16347,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15813,7 +16355,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15858,7 +16402,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -15866,7 +16410,9 @@
           <t>MPN429</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15911,7 +16457,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15919,7 +16465,9 @@
           <t>MPN033</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -15964,7 +16512,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15972,7 +16520,9 @@
           <t>MPN064</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16017,7 +16567,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -16025,7 +16575,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16070,7 +16622,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -16078,7 +16630,9 @@
           <t>MPN561</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>100</v>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16123,7 +16677,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16131,7 +16685,9 @@
           <t>MPN632</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16176,7 +16732,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -16184,7 +16740,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>100</v>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16229,7 +16787,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -16237,7 +16795,9 @@
           <t>MPN322-MPN324</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16282,7 +16842,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -16290,7 +16850,9 @@
           <t>MPN065</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16335,7 +16897,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -16343,7 +16905,9 @@
           <t>MPN561</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16388,7 +16952,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -16396,7 +16960,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>100</v>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16441,7 +17007,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -16449,7 +17015,9 @@
           <t>MPN476</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>100</v>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16494,7 +17062,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -16502,7 +17070,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>100</v>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16547,7 +17117,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -16555,7 +17125,9 @@
           <t>MPN322-MPN324</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>100</v>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16600,7 +17172,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -16608,7 +17180,9 @@
           <t>MPN386</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16653,7 +17227,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -16661,7 +17235,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16706,7 +17282,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -16714,7 +17290,9 @@
           <t>MPN476</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16759,7 +17337,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -16767,7 +17345,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>100</v>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16812,7 +17392,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -16820,7 +17400,9 @@
           <t>MPN065</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>100</v>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16865,7 +17447,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -16873,7 +17455,9 @@
           <t>MPN064</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>100</v>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16918,7 +17502,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -16926,7 +17510,9 @@
           <t>MPN044</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>100</v>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -16971,7 +17557,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -16979,7 +17565,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>100</v>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17024,7 +17612,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -17032,7 +17620,9 @@
           <t>MPN006</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>100</v>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17077,7 +17667,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -17085,7 +17675,9 @@
           <t>MPN320</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>100</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17130,7 +17722,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -17138,7 +17730,9 @@
           <t>MPN064</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>100</v>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17183,7 +17777,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -17191,7 +17785,9 @@
           <t>MPN044</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>100</v>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17236,7 +17832,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -17244,7 +17840,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17289,7 +17887,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -17297,7 +17895,9 @@
           <t>MPN006</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>100</v>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17342,7 +17942,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -17350,7 +17950,9 @@
           <t>MPN303</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>100</v>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17395,7 +17997,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -17403,7 +18005,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17448,7 +18052,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -17456,7 +18060,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>100</v>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17501,7 +18107,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -17509,7 +18115,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>100</v>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17554,7 +18162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -17562,7 +18170,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>100</v>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17607,7 +18217,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -17615,7 +18225,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17660,7 +18272,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -17668,7 +18280,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>100</v>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>1/s</t>
@@ -17713,7 +18327,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kcat (per s, NEEDS_CURATION)</t>
+          <t>kcat (per s, BACTERIAL_DEFAULT)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -17721,7 +18335,9 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>100</v>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>1/s</t>
